--- a/data/trans_orig/IP22D6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D6_2023-Clase-trans_orig.xlsx
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>7342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43048</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>95953</t>
+          <t>96233</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP22D6_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,74 +720,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5887</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3558</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>87,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,91%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5755</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6629</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>48,44%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4085</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>16</t>
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7342</t>
+          <t>6423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>3167</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,09%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3488</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6725</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4085</t>
+          <t>6629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,64 +1176,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5883</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5319</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4872</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>5647</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5319</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>10755</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,64 +1632,64 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>8101</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1707,7 +1707,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3379</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11480</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,64 +2088,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>12239</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>19880</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17798</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>17969</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37849</t>
+          <t>30037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,64 +2544,64 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>10575</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13083</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>12076</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>10146</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,64 +3000,64 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>3561</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,74 +3456,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>46589</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>43147</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>90,98%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>41390</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>38002</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>42264</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>52753</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>124</t>
@@ -3531,27 +3531,27 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>99343</t>
+          <t>89440</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96233</t>
+          <t>85969</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>4280</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>874</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>47427</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52753</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>100181</t>
+          <t>90314</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
